--- a/SDLC 2026 - BSI Control Testing/00 Reference/BSI.IT.23.C4 NewTest Script (proposed).xlsx
+++ b/SDLC 2026 - BSI Control Testing/00 Reference/BSI.IT.23.C4 NewTest Script (proposed).xlsx
@@ -594,7 +594,7 @@
 2. Validate Report Completeness and Accuracy
 Validate the completeness and accuracy of the application / release population against an independent source (ServiceNow release list, application inventory); obtain the query / filters and a screenshot of the extraction.
 3. Validate Population and Scope
-Annual control: select the annual occurrence (sample size 1 per RCSA methodology) and identify the applications / environments in scope (those used by SDLC projects in the period).
+Select the samples in accordance with the RCSA sampling methodology – the two SDLC projects provided in the evidence folder – and identify the applications / environments in scope (those used by SDLC projects in the period).
 4. Verify Control Execution
 Inspect evidence that development and QA environments are segregated from production (different server, IP, environment, repository) and that sampled releases were developed and tested in non-production before promotion through change management.
 5. Validate Control Results
